--- a/output/stock_quant_scores/GS_cash_flow_df.xlsx
+++ b/output/stock_quant_scores/GS_cash_flow_df.xlsx
@@ -1265,7 +1265,9 @@
       <c r="A6" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>1631000000</v>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
